--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.48136</v>
+        <v>16.64833</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0118</v>
+        <v>16.38262</v>
       </c>
       <c r="E2" t="n">
-        <v>16.75421</v>
+        <v>16.59178</v>
       </c>
       <c r="F2" t="n">
-        <v>41.26627</v>
+        <v>41.96856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05024</v>
+        <v>0.0509</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84253</v>
+        <v>1.82142</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.76672</v>
+        <v>16.77105</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63473</v>
+        <v>16.3772</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46045</v>
+        <v>16.71802</v>
       </c>
       <c r="F3" t="n">
-        <v>42.55825</v>
+        <v>41.98063</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05046</v>
+        <v>0.04951</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80386</v>
+        <v>1.78729</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.6419</v>
+        <v>17.02355</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55907</v>
+        <v>16.34453</v>
       </c>
       <c r="E4" t="n">
-        <v>16.68722</v>
+        <v>16.63435</v>
       </c>
       <c r="F4" t="n">
-        <v>42.70158</v>
+        <v>43.05543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04991</v>
+        <v>0.05006</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77523</v>
+        <v>1.78158</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.41484</v>
+        <v>16.58528</v>
       </c>
       <c r="D6" t="n">
-        <v>16.05412</v>
+        <v>15.92045</v>
       </c>
       <c r="E6" t="n">
-        <v>16.20889</v>
+        <v>16.25491</v>
       </c>
       <c r="F6" t="n">
-        <v>21.95651</v>
+        <v>21.92799</v>
       </c>
       <c r="G6" t="n">
-        <v>34.35547</v>
+        <v>34.26736</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.59653</v>
+        <v>16.65047</v>
       </c>
       <c r="D7" t="n">
-        <v>15.78964</v>
+        <v>15.84856</v>
       </c>
       <c r="E7" t="n">
-        <v>15.87591</v>
+        <v>16.41024</v>
       </c>
       <c r="F7" t="n">
-        <v>21.21141</v>
+        <v>22.1063</v>
       </c>
       <c r="G7" t="n">
-        <v>33.87183</v>
+        <v>33.78734</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.69224</v>
+        <v>16.39864</v>
       </c>
       <c r="D8" t="n">
-        <v>15.91206</v>
+        <v>15.85558</v>
       </c>
       <c r="E8" t="n">
-        <v>16.15708</v>
+        <v>16.31267</v>
       </c>
       <c r="F8" t="n">
-        <v>21.8387</v>
+        <v>21.97633</v>
       </c>
       <c r="G8" t="n">
-        <v>34.04461</v>
+        <v>34.28668</v>
       </c>
     </row>
   </sheetData>
